--- a/ig/notes/all-profiles.xlsx
+++ b/ig/notes/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-trial-use</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:54:36+00:00</t>
+    <t>2026-05-13T11:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
